--- a/portfolio/posts/_data/Pike_Chain_WQ_Data.xlsx
+++ b/portfolio/posts/_data/Pike_Chain_WQ_Data.xlsx
@@ -21,14 +21,14 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Comments!$A$1:$C$424</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">DO!$A$1:$J$1058</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Secchi!$A$1:$L$679</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Secchi!$A$1:$L$690</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9929" uniqueCount="483">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10004" uniqueCount="484">
   <si>
     <t>Buskey Bay</t>
   </si>
@@ -1478,6 +1478,9 @@
   <si>
     <t>WEX</t>
   </si>
+  <si>
+    <t>DHO / WEX</t>
+  </si>
 </sst>
 </file>
 
@@ -2333,8 +2336,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:L679"/>
+  <dimension ref="A1:L694"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.44140625" bestFit="1" customWidth="1"/>
@@ -2389,7 +2391,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="2" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -2415,7 +2417,7 @@
         <v>33450</v>
       </c>
     </row>
-    <row r="3" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -2435,7 +2437,7 @@
         <v>35578</v>
       </c>
     </row>
-    <row r="4" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -2455,7 +2457,7 @@
         <v>35649</v>
       </c>
     </row>
-    <row r="5" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>0</v>
       </c>
@@ -2484,7 +2486,7 @@
         <v>39197</v>
       </c>
     </row>
-    <row r="6" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>0</v>
       </c>
@@ -2513,7 +2515,7 @@
         <v>39258</v>
       </c>
     </row>
-    <row r="7" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>0</v>
       </c>
@@ -2542,7 +2544,7 @@
         <v>39287</v>
       </c>
     </row>
-    <row r="8" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>0</v>
       </c>
@@ -2571,7 +2573,7 @@
         <v>39322</v>
       </c>
     </row>
-    <row r="9" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>0</v>
       </c>
@@ -2600,7 +2602,7 @@
         <v>39394</v>
       </c>
     </row>
-    <row r="10" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>0</v>
       </c>
@@ -2623,7 +2625,7 @@
         <v>39499</v>
       </c>
     </row>
-    <row r="11" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>0</v>
       </c>
@@ -2646,7 +2648,7 @@
         <v>40030</v>
       </c>
     </row>
-    <row r="12" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>0</v>
       </c>
@@ -2669,7 +2671,7 @@
         <v>40051</v>
       </c>
     </row>
-    <row r="13" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>0</v>
       </c>
@@ -2692,7 +2694,7 @@
         <v>40063</v>
       </c>
     </row>
-    <row r="14" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>0</v>
       </c>
@@ -2715,7 +2717,7 @@
         <v>40349</v>
       </c>
     </row>
-    <row r="15" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>0</v>
       </c>
@@ -2738,7 +2740,7 @@
         <v>40373</v>
       </c>
     </row>
-    <row r="16" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>0</v>
       </c>
@@ -2761,7 +2763,7 @@
         <v>40396</v>
       </c>
     </row>
-    <row r="17" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>0</v>
       </c>
@@ -2787,7 +2789,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>0</v>
       </c>
@@ -2813,7 +2815,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>0</v>
       </c>
@@ -2836,7 +2838,7 @@
         <v>40733</v>
       </c>
     </row>
-    <row r="20" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>0</v>
       </c>
@@ -2859,7 +2861,7 @@
         <v>40740</v>
       </c>
     </row>
-    <row r="21" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>0</v>
       </c>
@@ -2882,7 +2884,7 @@
         <v>40757</v>
       </c>
     </row>
-    <row r="22" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>0</v>
       </c>
@@ -2905,7 +2907,7 @@
         <v>40783</v>
       </c>
     </row>
-    <row r="23" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>0</v>
       </c>
@@ -2928,7 +2930,7 @@
         <v>41091</v>
       </c>
     </row>
-    <row r="24" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>0</v>
       </c>
@@ -2951,7 +2953,7 @@
         <v>41111</v>
       </c>
     </row>
-    <row r="25" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>0</v>
       </c>
@@ -2974,7 +2976,7 @@
         <v>41148</v>
       </c>
     </row>
-    <row r="26" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>0</v>
       </c>
@@ -2997,7 +2999,7 @@
         <v>41470</v>
       </c>
     </row>
-    <row r="27" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>0</v>
       </c>
@@ -3023,7 +3025,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>0</v>
       </c>
@@ -3049,7 +3051,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>0</v>
       </c>
@@ -3075,7 +3077,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>0</v>
       </c>
@@ -3101,7 +3103,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>0</v>
       </c>
@@ -3124,7 +3126,7 @@
         <v>42195</v>
       </c>
     </row>
-    <row r="32" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>0</v>
       </c>
@@ -3147,7 +3149,7 @@
         <v>42206</v>
       </c>
     </row>
-    <row r="33" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>0</v>
       </c>
@@ -3170,7 +3172,7 @@
         <v>42211</v>
       </c>
     </row>
-    <row r="34" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>0</v>
       </c>
@@ -3193,7 +3195,7 @@
         <v>42566</v>
       </c>
     </row>
-    <row r="35" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>0</v>
       </c>
@@ -3216,7 +3218,7 @@
         <v>42582</v>
       </c>
     </row>
-    <row r="36" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>0</v>
       </c>
@@ -3242,7 +3244,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="37" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>0</v>
       </c>
@@ -3268,7 +3270,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="38" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>0</v>
       </c>
@@ -3291,7 +3293,7 @@
         <v>43312</v>
       </c>
     </row>
-    <row r="39" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>0</v>
       </c>
@@ -3314,7 +3316,7 @@
         <v>43657</v>
       </c>
     </row>
-    <row r="40" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>0</v>
       </c>
@@ -3337,7 +3339,7 @@
         <v>43670</v>
       </c>
     </row>
-    <row r="41" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>0</v>
       </c>
@@ -3360,7 +3362,7 @@
         <v>44393</v>
       </c>
     </row>
-    <row r="42" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>0</v>
       </c>
@@ -3386,7 +3388,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="43" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>0</v>
       </c>
@@ -3400,7 +3402,7 @@
         <v>44777</v>
       </c>
     </row>
-    <row r="44" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>59</v>
       </c>
@@ -3408,7 +3410,7 @@
         <v>33451</v>
       </c>
     </row>
-    <row r="45" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>59</v>
       </c>
@@ -3446,7 +3448,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>59</v>
       </c>
@@ -3466,7 +3468,7 @@
         <v>35578</v>
       </c>
     </row>
-    <row r="47" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>59</v>
       </c>
@@ -3486,7 +3488,7 @@
         <v>35649</v>
       </c>
     </row>
-    <row r="48" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>59</v>
       </c>
@@ -3509,7 +3511,7 @@
         <v>37898</v>
       </c>
     </row>
-    <row r="49" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>59</v>
       </c>
@@ -3532,7 +3534,7 @@
         <v>38168</v>
       </c>
     </row>
-    <row r="50" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>59</v>
       </c>
@@ -3555,7 +3557,7 @@
         <v>38179</v>
       </c>
     </row>
-    <row r="51" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>59</v>
       </c>
@@ -3578,7 +3580,7 @@
         <v>38187</v>
       </c>
     </row>
-    <row r="52" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>59</v>
       </c>
@@ -3601,7 +3603,7 @@
         <v>38196</v>
       </c>
     </row>
-    <row r="53" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>59</v>
       </c>
@@ -3624,7 +3626,7 @@
         <v>38202</v>
       </c>
     </row>
-    <row r="54" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>59</v>
       </c>
@@ -3647,7 +3649,7 @@
         <v>38214</v>
       </c>
     </row>
-    <row r="55" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>59</v>
       </c>
@@ -3670,7 +3672,7 @@
         <v>38228</v>
       </c>
     </row>
-    <row r="56" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>59</v>
       </c>
@@ -3693,7 +3695,7 @@
         <v>38253</v>
       </c>
     </row>
-    <row r="57" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>59</v>
       </c>
@@ -3722,7 +3724,7 @@
         <v>39197</v>
       </c>
     </row>
-    <row r="58" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>59</v>
       </c>
@@ -3751,7 +3753,7 @@
         <v>39258</v>
       </c>
     </row>
-    <row r="59" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>59</v>
       </c>
@@ -3780,7 +3782,7 @@
         <v>39287</v>
       </c>
     </row>
-    <row r="60" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>59</v>
       </c>
@@ -3809,7 +3811,7 @@
         <v>39322</v>
       </c>
     </row>
-    <row r="61" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>59</v>
       </c>
@@ -3838,7 +3840,7 @@
         <v>39394</v>
       </c>
     </row>
-    <row r="62" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>59</v>
       </c>
@@ -3861,7 +3863,7 @@
         <v>39499</v>
       </c>
     </row>
-    <row r="63" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>59</v>
       </c>
@@ -3884,7 +3886,7 @@
         <v>39964</v>
       </c>
     </row>
-    <row r="64" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>59</v>
       </c>
@@ -3907,7 +3909,7 @@
         <v>39974</v>
       </c>
     </row>
-    <row r="65" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>59</v>
       </c>
@@ -3930,7 +3932,7 @@
         <v>39981</v>
       </c>
     </row>
-    <row r="66" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>59</v>
       </c>
@@ -3956,7 +3958,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="67" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>59</v>
       </c>
@@ -3979,7 +3981,7 @@
         <v>40004</v>
       </c>
     </row>
-    <row r="68" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>59</v>
       </c>
@@ -4002,7 +4004,7 @@
         <v>40015</v>
       </c>
     </row>
-    <row r="69" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>59</v>
       </c>
@@ -4025,7 +4027,7 @@
         <v>40021</v>
       </c>
     </row>
-    <row r="70" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>59</v>
       </c>
@@ -4051,7 +4053,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="71" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>59</v>
       </c>
@@ -4077,7 +4079,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="72" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>59</v>
       </c>
@@ -4103,7 +4105,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="73" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>59</v>
       </c>
@@ -4129,7 +4131,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="74" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>59</v>
       </c>
@@ -4155,7 +4157,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="75" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>59</v>
       </c>
@@ -4178,7 +4180,7 @@
         <v>40332</v>
       </c>
     </row>
-    <row r="76" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>59</v>
       </c>
@@ -4201,7 +4203,7 @@
         <v>40344</v>
       </c>
     </row>
-    <row r="77" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>59</v>
       </c>
@@ -4224,7 +4226,7 @@
         <v>40353</v>
       </c>
     </row>
-    <row r="78" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>59</v>
       </c>
@@ -4247,7 +4249,7 @@
         <v>40362</v>
       </c>
     </row>
-    <row r="79" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>59</v>
       </c>
@@ -4273,7 +4275,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="80" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>59</v>
       </c>
@@ -4296,7 +4298,7 @@
         <v>40386</v>
       </c>
     </row>
-    <row r="81" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>59</v>
       </c>
@@ -4319,7 +4321,7 @@
         <v>40407</v>
       </c>
     </row>
-    <row r="82" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>59</v>
       </c>
@@ -4342,7 +4344,7 @@
         <v>40418</v>
       </c>
     </row>
-    <row r="83" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>59</v>
       </c>
@@ -4365,7 +4367,7 @@
         <v>40430</v>
       </c>
     </row>
-    <row r="84" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>59</v>
       </c>
@@ -4388,7 +4390,7 @@
         <v>40443</v>
       </c>
     </row>
-    <row r="85" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>59</v>
       </c>
@@ -4411,7 +4413,7 @@
         <v>40705</v>
       </c>
     </row>
-    <row r="86" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>59</v>
       </c>
@@ -4434,7 +4436,7 @@
         <v>40721</v>
       </c>
     </row>
-    <row r="87" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>59</v>
       </c>
@@ -4457,7 +4459,7 @@
         <v>40728</v>
       </c>
     </row>
-    <row r="88" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>59</v>
       </c>
@@ -4480,7 +4482,7 @@
         <v>40736</v>
       </c>
     </row>
-    <row r="89" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>59</v>
       </c>
@@ -4503,7 +4505,7 @@
         <v>40746</v>
       </c>
     </row>
-    <row r="90" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>59</v>
       </c>
@@ -4526,7 +4528,7 @@
         <v>40757</v>
       </c>
     </row>
-    <row r="91" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>59</v>
       </c>
@@ -4549,7 +4551,7 @@
         <v>40769</v>
       </c>
     </row>
-    <row r="92" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>59</v>
       </c>
@@ -4575,7 +4577,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="93" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>59</v>
       </c>
@@ -4601,7 +4603,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="94" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>59</v>
       </c>
@@ -4627,7 +4629,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="95" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>59</v>
       </c>
@@ -4653,7 +4655,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="96" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>59</v>
       </c>
@@ -4679,7 +4681,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="97" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>59</v>
       </c>
@@ -4705,7 +4707,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="98" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>59</v>
       </c>
@@ -4728,7 +4730,7 @@
         <v>41107</v>
       </c>
     </row>
-    <row r="99" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>59</v>
       </c>
@@ -4763,7 +4765,7 @@
         <v>41114</v>
       </c>
     </row>
-    <row r="100" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>59</v>
       </c>
@@ -4783,7 +4785,7 @@
         <v>41125</v>
       </c>
     </row>
-    <row r="101" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>59</v>
       </c>
@@ -4806,7 +4808,7 @@
         <v>41141</v>
       </c>
     </row>
-    <row r="102" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>59</v>
       </c>
@@ -4841,7 +4843,7 @@
         <v>41148</v>
       </c>
     </row>
-    <row r="103" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>59</v>
       </c>
@@ -4867,7 +4869,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="104" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>59</v>
       </c>
@@ -4893,7 +4895,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="105" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>59</v>
       </c>
@@ -4931,7 +4933,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="106" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>59</v>
       </c>
@@ -4957,7 +4959,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="107" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>59</v>
       </c>
@@ -4983,7 +4985,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="108" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>59</v>
       </c>
@@ -5021,7 +5023,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="109" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>59</v>
       </c>
@@ -5047,7 +5049,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="110" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>59</v>
       </c>
@@ -5073,7 +5075,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="111" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>59</v>
       </c>
@@ -5099,7 +5101,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="112" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>59</v>
       </c>
@@ -5137,7 +5139,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="113" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>59</v>
       </c>
@@ -5160,7 +5162,7 @@
         <v>41524</v>
       </c>
     </row>
-    <row r="114" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>59</v>
       </c>
@@ -5183,7 +5185,7 @@
         <v>41540</v>
       </c>
     </row>
-    <row r="115" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>59</v>
       </c>
@@ -5215,7 +5217,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="116" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>59</v>
       </c>
@@ -5241,7 +5243,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="117" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>59</v>
       </c>
@@ -5267,7 +5269,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="118" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>59</v>
       </c>
@@ -5305,7 +5307,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="119" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>59</v>
       </c>
@@ -5331,7 +5333,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="120" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>59</v>
       </c>
@@ -5357,7 +5359,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="121" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>59</v>
       </c>
@@ -5383,7 +5385,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="122" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>59</v>
       </c>
@@ -5421,7 +5423,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="123" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>59</v>
       </c>
@@ -5447,7 +5449,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="124" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>59</v>
       </c>
@@ -5473,7 +5475,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="125" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>59</v>
       </c>
@@ -5511,7 +5513,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="126" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>59</v>
       </c>
@@ -5537,7 +5539,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="127" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>59</v>
       </c>
@@ -5563,7 +5565,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="128" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>59</v>
       </c>
@@ -5589,7 +5591,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="129" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>59</v>
       </c>
@@ -5627,7 +5629,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="130" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>59</v>
       </c>
@@ -5650,7 +5652,7 @@
         <v>42192</v>
       </c>
     </row>
-    <row r="131" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>59</v>
       </c>
@@ -5676,7 +5678,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="132" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>59</v>
       </c>
@@ -5711,7 +5713,7 @@
         <v>42212</v>
       </c>
     </row>
-    <row r="133" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>59</v>
       </c>
@@ -5734,7 +5736,7 @@
         <v>42228</v>
       </c>
     </row>
-    <row r="134" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>59</v>
       </c>
@@ -5772,7 +5774,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="135" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>59</v>
       </c>
@@ -5798,7 +5800,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="136" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>59</v>
       </c>
@@ -5824,7 +5826,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="137" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>59</v>
       </c>
@@ -5850,7 +5852,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="138" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>59</v>
       </c>
@@ -5870,7 +5872,7 @@
         <v>42548</v>
       </c>
     </row>
-    <row r="139" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>59</v>
       </c>
@@ -5905,7 +5907,7 @@
         <v>42578</v>
       </c>
     </row>
-    <row r="140" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>59</v>
       </c>
@@ -5940,7 +5942,7 @@
         <v>42605</v>
       </c>
     </row>
-    <row r="141" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>59</v>
       </c>
@@ -5948,7 +5950,7 @@
         <v>42893</v>
       </c>
     </row>
-    <row r="142" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>59</v>
       </c>
@@ -5956,7 +5958,7 @@
         <v>42895</v>
       </c>
     </row>
-    <row r="143" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>59</v>
       </c>
@@ -5964,7 +5966,7 @@
         <v>42897</v>
       </c>
     </row>
-    <row r="144" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>59</v>
       </c>
@@ -5987,7 +5989,7 @@
         <v>42898</v>
       </c>
     </row>
-    <row r="145" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>59</v>
       </c>
@@ -5995,7 +5997,7 @@
         <v>42899</v>
       </c>
     </row>
-    <row r="146" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>59</v>
       </c>
@@ -6021,7 +6023,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="147" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>59</v>
       </c>
@@ -6029,7 +6031,7 @@
         <v>42906</v>
       </c>
     </row>
-    <row r="148" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>59</v>
       </c>
@@ -6049,7 +6051,7 @@
         <v>42906</v>
       </c>
     </row>
-    <row r="149" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>59</v>
       </c>
@@ -6057,7 +6059,7 @@
         <v>42913</v>
       </c>
     </row>
-    <row r="150" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>59</v>
       </c>
@@ -6083,7 +6085,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="151" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>59</v>
       </c>
@@ -6091,7 +6093,7 @@
         <v>42921</v>
       </c>
     </row>
-    <row r="152" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>59</v>
       </c>
@@ -6114,7 +6116,7 @@
         <v>42926</v>
       </c>
     </row>
-    <row r="153" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>59</v>
       </c>
@@ -6122,7 +6124,7 @@
         <v>42927</v>
       </c>
     </row>
-    <row r="154" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>59</v>
       </c>
@@ -6157,7 +6159,7 @@
         <v>42940</v>
       </c>
     </row>
-    <row r="155" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>59</v>
       </c>
@@ -6177,7 +6179,7 @@
         <v>42975</v>
       </c>
     </row>
-    <row r="156" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>59</v>
       </c>
@@ -6203,7 +6205,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="157" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>59</v>
       </c>
@@ -6229,7 +6231,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="158" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>59</v>
       </c>
@@ -6252,7 +6254,7 @@
         <v>43228</v>
       </c>
     </row>
-    <row r="159" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>59</v>
       </c>
@@ -6284,7 +6286,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="160" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>59</v>
       </c>
@@ -6304,7 +6306,7 @@
         <v>43277</v>
       </c>
     </row>
-    <row r="161" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>59</v>
       </c>
@@ -6327,7 +6329,7 @@
         <v>43281</v>
       </c>
     </row>
-    <row r="162" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>59</v>
       </c>
@@ -6359,7 +6361,7 @@
         <v>43297</v>
       </c>
     </row>
-    <row r="163" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>59</v>
       </c>
@@ -6379,7 +6381,7 @@
         <v>43302</v>
       </c>
     </row>
-    <row r="164" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>59</v>
       </c>
@@ -6414,7 +6416,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="165" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>59</v>
       </c>
@@ -6428,7 +6430,7 @@
         <v>43620</v>
       </c>
     </row>
-    <row r="166" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>59</v>
       </c>
@@ -6454,7 +6456,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="167" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>59</v>
       </c>
@@ -6462,7 +6464,7 @@
         <v>43627</v>
       </c>
     </row>
-    <row r="168" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>59</v>
       </c>
@@ -6470,7 +6472,7 @@
         <v>43629</v>
       </c>
     </row>
-    <row r="169" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>59</v>
       </c>
@@ -6478,7 +6480,7 @@
         <v>43631</v>
       </c>
     </row>
-    <row r="170" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>59</v>
       </c>
@@ -6486,7 +6488,7 @@
         <v>43633</v>
       </c>
     </row>
-    <row r="171" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>59</v>
       </c>
@@ -6494,7 +6496,7 @@
         <v>43636</v>
       </c>
     </row>
-    <row r="172" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>59</v>
       </c>
@@ -6502,7 +6504,7 @@
         <v>43640</v>
       </c>
     </row>
-    <row r="173" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>59</v>
       </c>
@@ -6537,7 +6539,7 @@
         <v>43641</v>
       </c>
     </row>
-    <row r="174" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>59</v>
       </c>
@@ -6545,7 +6547,7 @@
         <v>43647</v>
       </c>
     </row>
-    <row r="175" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>59</v>
       </c>
@@ -6553,7 +6555,7 @@
         <v>43654</v>
       </c>
     </row>
-    <row r="176" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>59</v>
       </c>
@@ -6576,7 +6578,7 @@
         <v>43660</v>
       </c>
     </row>
-    <row r="177" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>59</v>
       </c>
@@ -6584,7 +6586,7 @@
         <v>43661</v>
       </c>
     </row>
-    <row r="178" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>59</v>
       </c>
@@ -6592,7 +6594,7 @@
         <v>43668</v>
       </c>
     </row>
-    <row r="179" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>59</v>
       </c>
@@ -6615,7 +6617,7 @@
         <v>43668</v>
       </c>
     </row>
-    <row r="180" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>59</v>
       </c>
@@ -6635,7 +6637,7 @@
         <v>43669</v>
       </c>
     </row>
-    <row r="181" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>59</v>
       </c>
@@ -6643,7 +6645,7 @@
         <v>43675</v>
       </c>
     </row>
-    <row r="182" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>59</v>
       </c>
@@ -6666,7 +6668,7 @@
         <v>43685</v>
       </c>
     </row>
-    <row r="183" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>59</v>
       </c>
@@ -6674,7 +6676,7 @@
         <v>43696</v>
       </c>
     </row>
-    <row r="184" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>59</v>
       </c>
@@ -6709,7 +6711,7 @@
         <v>43703</v>
       </c>
     </row>
-    <row r="185" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>59</v>
       </c>
@@ -6732,7 +6734,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="186" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>59</v>
       </c>
@@ -6767,7 +6769,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="187" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>59</v>
       </c>
@@ -6802,7 +6804,7 @@
         <v>44032</v>
       </c>
     </row>
-    <row r="188" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>59</v>
       </c>
@@ -6825,7 +6827,7 @@
         <v>44047</v>
       </c>
     </row>
-    <row r="189" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>59</v>
       </c>
@@ -6860,7 +6862,7 @@
         <v>44060</v>
       </c>
     </row>
-    <row r="190" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>59</v>
       </c>
@@ -6880,7 +6882,7 @@
         <v>44069</v>
       </c>
     </row>
-    <row r="191" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>59</v>
       </c>
@@ -6903,7 +6905,7 @@
         <v>44079</v>
       </c>
     </row>
-    <row r="192" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>59</v>
       </c>
@@ -6926,7 +6928,7 @@
         <v>44096</v>
       </c>
     </row>
-    <row r="193" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>59</v>
       </c>
@@ -6949,7 +6951,7 @@
         <v>44108</v>
       </c>
     </row>
-    <row r="194" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>59</v>
       </c>
@@ -6972,7 +6974,7 @@
         <v>44120</v>
       </c>
     </row>
-    <row r="195" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>59</v>
       </c>
@@ -7001,7 +7003,7 @@
         <v>44319</v>
       </c>
     </row>
-    <row r="196" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>59</v>
       </c>
@@ -7036,7 +7038,7 @@
         <v>44362</v>
       </c>
     </row>
-    <row r="197" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>59</v>
       </c>
@@ -7059,7 +7061,7 @@
         <v>44372</v>
       </c>
     </row>
-    <row r="198" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>59</v>
       </c>
@@ -7082,7 +7084,7 @@
         <v>44382</v>
       </c>
     </row>
-    <row r="199" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>59</v>
       </c>
@@ -7099,7 +7101,7 @@
         <v>44385</v>
       </c>
     </row>
-    <row r="200" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>59</v>
       </c>
@@ -7122,7 +7124,7 @@
         <v>44386</v>
       </c>
     </row>
-    <row r="201" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>59</v>
       </c>
@@ -7157,7 +7159,7 @@
         <v>44396</v>
       </c>
     </row>
-    <row r="202" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>59</v>
       </c>
@@ -7180,7 +7182,7 @@
         <v>44407</v>
       </c>
     </row>
-    <row r="203" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>59</v>
       </c>
@@ -7215,7 +7217,7 @@
         <v>44425</v>
       </c>
     </row>
-    <row r="204" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>59</v>
       </c>
@@ -7235,7 +7237,7 @@
         <v>44438</v>
       </c>
     </row>
-    <row r="205" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>59</v>
       </c>
@@ -7255,7 +7257,7 @@
         <v>44445</v>
       </c>
     </row>
-    <row r="206" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>59</v>
       </c>
@@ -7278,7 +7280,7 @@
         <v>44456</v>
       </c>
     </row>
-    <row r="207" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>59</v>
       </c>
@@ -7298,7 +7300,7 @@
         <v>44724</v>
       </c>
     </row>
-    <row r="208" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>59</v>
       </c>
@@ -7333,7 +7335,7 @@
         <v>44734</v>
       </c>
     </row>
-    <row r="209" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>59</v>
       </c>
@@ -7353,7 +7355,7 @@
         <v>44744</v>
       </c>
     </row>
-    <row r="210" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>59</v>
       </c>
@@ -7376,7 +7378,7 @@
         <v>44757</v>
       </c>
     </row>
-    <row r="211" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>59</v>
       </c>
@@ -7396,7 +7398,7 @@
         <v>44760</v>
       </c>
     </row>
-    <row r="212" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>59</v>
       </c>
@@ -7416,7 +7418,7 @@
         <v>44771</v>
       </c>
     </row>
-    <row r="213" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>59</v>
       </c>
@@ -7439,7 +7441,7 @@
         <v>44783</v>
       </c>
     </row>
-    <row r="214" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>59</v>
       </c>
@@ -7462,7 +7464,7 @@
         <v>44798</v>
       </c>
     </row>
-    <row r="215" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>59</v>
       </c>
@@ -7482,7 +7484,7 @@
         <v>44810</v>
       </c>
     </row>
-    <row r="216" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>184</v>
       </c>
@@ -7502,7 +7504,7 @@
         <v>33451</v>
       </c>
     </row>
-    <row r="217" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>184</v>
       </c>
@@ -7525,7 +7527,7 @@
         <v>37898</v>
       </c>
     </row>
-    <row r="218" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>184</v>
       </c>
@@ -7548,7 +7550,7 @@
         <v>38168</v>
       </c>
     </row>
-    <row r="219" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>184</v>
       </c>
@@ -7571,7 +7573,7 @@
         <v>38179</v>
       </c>
     </row>
-    <row r="220" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>184</v>
       </c>
@@ -7594,7 +7596,7 @@
         <v>38187</v>
       </c>
     </row>
-    <row r="221" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>184</v>
       </c>
@@ -7617,7 +7619,7 @@
         <v>38196</v>
       </c>
     </row>
-    <row r="222" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>184</v>
       </c>
@@ -7640,7 +7642,7 @@
         <v>38214</v>
       </c>
     </row>
-    <row r="223" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>184</v>
       </c>
@@ -7663,7 +7665,7 @@
         <v>38228</v>
       </c>
     </row>
-    <row r="224" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>184</v>
       </c>
@@ -7686,7 +7688,7 @@
         <v>38253</v>
       </c>
     </row>
-    <row r="225" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>184</v>
       </c>
@@ -7715,7 +7717,7 @@
         <v>39197</v>
       </c>
     </row>
-    <row r="226" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>184</v>
       </c>
@@ -7744,7 +7746,7 @@
         <v>39258</v>
       </c>
     </row>
-    <row r="227" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>184</v>
       </c>
@@ -7773,7 +7775,7 @@
         <v>39287</v>
       </c>
     </row>
-    <row r="228" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>184</v>
       </c>
@@ -7802,7 +7804,7 @@
         <v>39322</v>
       </c>
     </row>
-    <row r="229" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>184</v>
       </c>
@@ -7831,7 +7833,7 @@
         <v>39394</v>
       </c>
     </row>
-    <row r="230" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>184</v>
       </c>
@@ -7854,7 +7856,7 @@
         <v>39499</v>
       </c>
     </row>
-    <row r="231" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>184</v>
       </c>
@@ -7877,7 +7879,7 @@
         <v>39964</v>
       </c>
     </row>
-    <row r="232" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>184</v>
       </c>
@@ -7900,7 +7902,7 @@
         <v>39974</v>
       </c>
     </row>
-    <row r="233" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>184</v>
       </c>
@@ -7923,7 +7925,7 @@
         <v>39981</v>
       </c>
     </row>
-    <row r="234" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>184</v>
       </c>
@@ -7946,7 +7948,7 @@
         <v>40004</v>
       </c>
     </row>
-    <row r="235" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>184</v>
       </c>
@@ -7969,7 +7971,7 @@
         <v>40015</v>
       </c>
     </row>
-    <row r="236" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>184</v>
       </c>
@@ -7992,7 +7994,7 @@
         <v>40043</v>
       </c>
     </row>
-    <row r="237" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>184</v>
       </c>
@@ -8015,7 +8017,7 @@
         <v>40055</v>
       </c>
     </row>
-    <row r="238" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>184</v>
       </c>
@@ -8038,7 +8040,7 @@
         <v>40335</v>
       </c>
     </row>
-    <row r="239" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>184</v>
       </c>
@@ -8061,7 +8063,7 @@
         <v>40353</v>
       </c>
     </row>
-    <row r="240" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>184</v>
       </c>
@@ -8084,7 +8086,7 @@
         <v>40386</v>
       </c>
     </row>
-    <row r="241" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>184</v>
       </c>
@@ -8107,7 +8109,7 @@
         <v>40418</v>
       </c>
     </row>
-    <row r="242" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>184</v>
       </c>
@@ -8130,7 +8132,7 @@
         <v>40705</v>
       </c>
     </row>
-    <row r="243" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>184</v>
       </c>
@@ -8153,7 +8155,7 @@
         <v>40728</v>
       </c>
     </row>
-    <row r="244" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>184</v>
       </c>
@@ -8176,7 +8178,7 @@
         <v>40769</v>
       </c>
     </row>
-    <row r="245" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>184</v>
       </c>
@@ -8199,7 +8201,7 @@
         <v>40802</v>
       </c>
     </row>
-    <row r="246" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>184</v>
       </c>
@@ -8222,7 +8224,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="247" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>184</v>
       </c>
@@ -8248,7 +8250,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="248" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>184</v>
       </c>
@@ -8271,7 +8273,7 @@
         <v>41125</v>
       </c>
     </row>
-    <row r="249" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>184</v>
       </c>
@@ -8294,7 +8296,7 @@
         <v>41148</v>
       </c>
     </row>
-    <row r="250" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>184</v>
       </c>
@@ -8320,7 +8322,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="251" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>184</v>
       </c>
@@ -8346,7 +8348,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="252" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>184</v>
       </c>
@@ -8372,7 +8374,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="253" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>184</v>
       </c>
@@ -8398,7 +8400,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="254" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
         <v>184</v>
       </c>
@@ -8424,7 +8426,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="255" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
         <v>184</v>
       </c>
@@ -8450,7 +8452,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="256" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
         <v>184</v>
       </c>
@@ -8476,7 +8478,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="257" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>184</v>
       </c>
@@ -8502,7 +8504,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="258" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
         <v>184</v>
       </c>
@@ -8528,7 +8530,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="259" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
         <v>184</v>
       </c>
@@ -8554,7 +8556,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="260" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>184</v>
       </c>
@@ -8580,7 +8582,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="261" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
         <v>184</v>
       </c>
@@ -8600,7 +8602,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="262" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
         <v>184</v>
       </c>
@@ -8623,7 +8625,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="263" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
         <v>184</v>
       </c>
@@ -8643,7 +8645,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="264" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
         <v>184</v>
       </c>
@@ -8651,7 +8653,7 @@
         <v>42893</v>
       </c>
     </row>
-    <row r="265" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
         <v>184</v>
       </c>
@@ -8659,7 +8661,7 @@
         <v>42895</v>
       </c>
     </row>
-    <row r="266" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
         <v>184</v>
       </c>
@@ -8667,7 +8669,7 @@
         <v>42897</v>
       </c>
     </row>
-    <row r="267" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>184</v>
       </c>
@@ -8690,7 +8692,7 @@
         <v>42898</v>
       </c>
     </row>
-    <row r="268" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>184</v>
       </c>
@@ -8698,7 +8700,7 @@
         <v>42899</v>
       </c>
     </row>
-    <row r="269" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
         <v>184</v>
       </c>
@@ -8721,7 +8723,7 @@
         <v>42905</v>
       </c>
     </row>
-    <row r="270" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
         <v>184</v>
       </c>
@@ -8729,7 +8731,7 @@
         <v>42906</v>
       </c>
     </row>
-    <row r="271" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>184</v>
       </c>
@@ -8737,7 +8739,7 @@
         <v>42913</v>
       </c>
     </row>
-    <row r="272" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
         <v>184</v>
       </c>
@@ -8760,7 +8762,7 @@
         <v>42913</v>
       </c>
     </row>
-    <row r="273" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>184</v>
       </c>
@@ -8768,7 +8770,7 @@
         <v>42921</v>
       </c>
     </row>
-    <row r="274" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
         <v>184</v>
       </c>
@@ -8776,7 +8778,7 @@
         <v>42927</v>
       </c>
     </row>
-    <row r="275" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
         <v>184</v>
       </c>
@@ -8799,7 +8801,7 @@
         <v>42999</v>
       </c>
     </row>
-    <row r="276" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
         <v>184</v>
       </c>
@@ -8819,7 +8821,7 @@
         <v>43297</v>
       </c>
     </row>
-    <row r="277" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
         <v>184</v>
       </c>
@@ -8827,7 +8829,7 @@
         <v>43629</v>
       </c>
     </row>
-    <row r="278" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
         <v>184</v>
       </c>
@@ -8835,7 +8837,7 @@
         <v>43633</v>
       </c>
     </row>
-    <row r="279" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
         <v>184</v>
       </c>
@@ -8858,7 +8860,7 @@
         <v>43641</v>
       </c>
     </row>
-    <row r="280" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
         <v>184</v>
       </c>
@@ -8866,7 +8868,7 @@
         <v>43647</v>
       </c>
     </row>
-    <row r="281" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
         <v>184</v>
       </c>
@@ -8889,7 +8891,7 @@
         <v>43660</v>
       </c>
     </row>
-    <row r="282" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
         <v>184</v>
       </c>
@@ -8912,7 +8914,7 @@
         <v>43668</v>
       </c>
     </row>
-    <row r="283" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
         <v>184</v>
       </c>
@@ -8935,7 +8937,7 @@
         <v>43703</v>
       </c>
     </row>
-    <row r="284" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
         <v>184</v>
       </c>
@@ -8958,7 +8960,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="285" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
         <v>184</v>
       </c>
@@ -8981,7 +8983,7 @@
         <v>44032</v>
       </c>
     </row>
-    <row r="286" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
         <v>184</v>
       </c>
@@ -9004,7 +9006,7 @@
         <v>44047</v>
       </c>
     </row>
-    <row r="287" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
         <v>184</v>
       </c>
@@ -9024,7 +9026,7 @@
         <v>44060</v>
       </c>
     </row>
-    <row r="288" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
         <v>184</v>
       </c>
@@ -9047,7 +9049,7 @@
         <v>44079</v>
       </c>
     </row>
-    <row r="289" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
         <v>184</v>
       </c>
@@ -9070,7 +9072,7 @@
         <v>44096</v>
       </c>
     </row>
-    <row r="290" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
         <v>184</v>
       </c>
@@ -9093,7 +9095,7 @@
         <v>44108</v>
       </c>
     </row>
-    <row r="291" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
         <v>184</v>
       </c>
@@ -9116,7 +9118,7 @@
         <v>44120</v>
       </c>
     </row>
-    <row r="292" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
         <v>184</v>
       </c>
@@ -9139,7 +9141,7 @@
         <v>44385</v>
       </c>
     </row>
-    <row r="293" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
         <v>184</v>
       </c>
@@ -9159,7 +9161,7 @@
         <v>44396</v>
       </c>
     </row>
-    <row r="294" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
         <v>184</v>
       </c>
@@ -9182,7 +9184,7 @@
         <v>44438</v>
       </c>
     </row>
-    <row r="295" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
         <v>184</v>
       </c>
@@ -9202,7 +9204,7 @@
         <v>45078</v>
       </c>
     </row>
-    <row r="296" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
         <v>217</v>
       </c>
@@ -9228,7 +9230,7 @@
         <v>33450</v>
       </c>
     </row>
-    <row r="297" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
         <v>217</v>
       </c>
@@ -9251,7 +9253,7 @@
         <v>34170</v>
       </c>
     </row>
-    <row r="298" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
         <v>217</v>
       </c>
@@ -9274,7 +9276,7 @@
         <v>34197</v>
       </c>
     </row>
-    <row r="299" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
         <v>217</v>
       </c>
@@ -9297,7 +9299,7 @@
         <v>34230</v>
       </c>
     </row>
-    <row r="300" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
         <v>217</v>
       </c>
@@ -9320,7 +9322,7 @@
         <v>34262</v>
       </c>
     </row>
-    <row r="301" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
         <v>217</v>
       </c>
@@ -9340,7 +9342,7 @@
         <v>35578</v>
       </c>
     </row>
-    <row r="302" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
         <v>217</v>
       </c>
@@ -9360,7 +9362,7 @@
         <v>35649</v>
       </c>
     </row>
-    <row r="303" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
         <v>217</v>
       </c>
@@ -9383,7 +9385,7 @@
         <v>37898</v>
       </c>
     </row>
-    <row r="304" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
         <v>217</v>
       </c>
@@ -9406,7 +9408,7 @@
         <v>38168</v>
       </c>
     </row>
-    <row r="305" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
         <v>217</v>
       </c>
@@ -9429,7 +9431,7 @@
         <v>38179</v>
       </c>
     </row>
-    <row r="306" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
         <v>217</v>
       </c>
@@ -9452,7 +9454,7 @@
         <v>38187</v>
       </c>
     </row>
-    <row r="307" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
         <v>217</v>
       </c>
@@ -9475,7 +9477,7 @@
         <v>38196</v>
       </c>
     </row>
-    <row r="308" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
         <v>217</v>
       </c>
@@ -9498,7 +9500,7 @@
         <v>38202</v>
       </c>
     </row>
-    <row r="309" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
         <v>217</v>
       </c>
@@ -9521,7 +9523,7 @@
         <v>38228</v>
       </c>
     </row>
-    <row r="310" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
         <v>217</v>
       </c>
@@ -9544,7 +9546,7 @@
         <v>38253</v>
       </c>
     </row>
-    <row r="311" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
         <v>217</v>
       </c>
@@ -9573,7 +9575,7 @@
         <v>39197</v>
       </c>
     </row>
-    <row r="312" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
         <v>217</v>
       </c>
@@ -9602,7 +9604,7 @@
         <v>39258</v>
       </c>
     </row>
-    <row r="313" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
         <v>217</v>
       </c>
@@ -9631,7 +9633,7 @@
         <v>39287</v>
       </c>
     </row>
-    <row r="314" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
         <v>217</v>
       </c>
@@ -9660,7 +9662,7 @@
         <v>39322</v>
       </c>
     </row>
-    <row r="315" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
         <v>217</v>
       </c>
@@ -9689,7 +9691,7 @@
         <v>39394</v>
       </c>
     </row>
-    <row r="316" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
         <v>217</v>
       </c>
@@ -9712,7 +9714,7 @@
         <v>39499</v>
       </c>
     </row>
-    <row r="317" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
         <v>217</v>
       </c>
@@ -9735,7 +9737,7 @@
         <v>39978</v>
       </c>
     </row>
-    <row r="318" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
         <v>217</v>
       </c>
@@ -9758,7 +9760,7 @@
         <v>40007</v>
       </c>
     </row>
-    <row r="319" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
         <v>217</v>
       </c>
@@ -9781,7 +9783,7 @@
         <v>40020</v>
       </c>
     </row>
-    <row r="320" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
         <v>217</v>
       </c>
@@ -9804,7 +9806,7 @@
         <v>40030</v>
       </c>
     </row>
-    <row r="321" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
         <v>217</v>
       </c>
@@ -9827,7 +9829,7 @@
         <v>40038</v>
       </c>
     </row>
-    <row r="322" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
         <v>217</v>
       </c>
@@ -9850,7 +9852,7 @@
         <v>40049</v>
       </c>
     </row>
-    <row r="323" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
         <v>217</v>
       </c>
@@ -9873,7 +9875,7 @@
         <v>40063</v>
       </c>
     </row>
-    <row r="324" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
         <v>217</v>
       </c>
@@ -9896,7 +9898,7 @@
         <v>40079</v>
       </c>
     </row>
-    <row r="325" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
         <v>217</v>
       </c>
@@ -9904,7 +9906,7 @@
         <v>40405</v>
       </c>
     </row>
-    <row r="326" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
         <v>217</v>
       </c>
@@ -9927,7 +9929,7 @@
         <v>41856</v>
       </c>
     </row>
-    <row r="327" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
         <v>217</v>
       </c>
@@ -9938,7 +9940,7 @@
         <v>41857</v>
       </c>
     </row>
-    <row r="328" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
         <v>217</v>
       </c>
@@ -9961,7 +9963,7 @@
         <v>41871</v>
       </c>
     </row>
-    <row r="329" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
         <v>217</v>
       </c>
@@ -9984,7 +9986,7 @@
         <v>41891</v>
       </c>
     </row>
-    <row r="330" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
         <v>217</v>
       </c>
@@ -10007,7 +10009,7 @@
         <v>41906</v>
       </c>
     </row>
-    <row r="331" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
         <v>217</v>
       </c>
@@ -10015,7 +10017,7 @@
         <v>42893</v>
       </c>
     </row>
-    <row r="332" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
         <v>217</v>
       </c>
@@ -10023,7 +10025,7 @@
         <v>42895</v>
       </c>
     </row>
-    <row r="333" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
         <v>217</v>
       </c>
@@ -10031,7 +10033,7 @@
         <v>42897</v>
       </c>
     </row>
-    <row r="334" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
         <v>217</v>
       </c>
@@ -10039,7 +10041,7 @@
         <v>42899</v>
       </c>
     </row>
-    <row r="335" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
         <v>217</v>
       </c>
@@ -10047,7 +10049,7 @@
         <v>42906</v>
       </c>
     </row>
-    <row r="336" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
         <v>217</v>
       </c>
@@ -10055,7 +10057,7 @@
         <v>42913</v>
       </c>
     </row>
-    <row r="337" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
         <v>217</v>
       </c>
@@ -10063,7 +10065,7 @@
         <v>42921</v>
       </c>
     </row>
-    <row r="338" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
         <v>217</v>
       </c>
@@ -10071,7 +10073,7 @@
         <v>42927</v>
       </c>
     </row>
-    <row r="339" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
         <v>217</v>
       </c>
@@ -10094,7 +10096,7 @@
         <v>43275</v>
       </c>
     </row>
-    <row r="340" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
         <v>217</v>
       </c>
@@ -10117,7 +10119,7 @@
         <v>43286</v>
       </c>
     </row>
-    <row r="341" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
         <v>217</v>
       </c>
@@ -10140,7 +10142,7 @@
         <v>43310</v>
       </c>
     </row>
-    <row r="342" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
         <v>217</v>
       </c>
@@ -10163,7 +10165,7 @@
         <v>43346</v>
       </c>
     </row>
-    <row r="343" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
         <v>217</v>
       </c>
@@ -10186,7 +10188,7 @@
         <v>43670</v>
       </c>
     </row>
-    <row r="344" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
         <v>217</v>
       </c>
@@ -10209,7 +10211,7 @@
         <v>43734</v>
       </c>
     </row>
-    <row r="345" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
         <v>217</v>
       </c>
@@ -10232,7 +10234,7 @@
         <v>43742</v>
       </c>
     </row>
-    <row r="346" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
         <v>217</v>
       </c>
@@ -10255,7 +10257,7 @@
         <v>43982</v>
       </c>
     </row>
-    <row r="347" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
         <v>217</v>
       </c>
@@ -10278,7 +10280,7 @@
         <v>44006</v>
       </c>
     </row>
-    <row r="348" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
         <v>217</v>
       </c>
@@ -10301,7 +10303,7 @@
         <v>44054</v>
       </c>
     </row>
-    <row r="349" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
         <v>217</v>
       </c>
@@ -10324,7 +10326,7 @@
         <v>44110</v>
       </c>
     </row>
-    <row r="350" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
         <v>217</v>
       </c>
@@ -10347,7 +10349,7 @@
         <v>44374</v>
       </c>
     </row>
-    <row r="351" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
         <v>217</v>
       </c>
@@ -10370,7 +10372,7 @@
         <v>44390</v>
       </c>
     </row>
-    <row r="352" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
         <v>217</v>
       </c>
@@ -10393,7 +10395,7 @@
         <v>44430</v>
       </c>
     </row>
-    <row r="353" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
         <v>217</v>
       </c>
@@ -10416,7 +10418,7 @@
         <v>44478</v>
       </c>
     </row>
-    <row r="354" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
         <v>217</v>
       </c>
@@ -10439,7 +10441,7 @@
         <v>44734</v>
       </c>
     </row>
-    <row r="355" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
         <v>217</v>
       </c>
@@ -10462,7 +10464,7 @@
         <v>44798</v>
       </c>
     </row>
-    <row r="356" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
         <v>217</v>
       </c>
@@ -10485,7 +10487,7 @@
         <v>44806</v>
       </c>
     </row>
-    <row r="357" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
         <v>217</v>
       </c>
@@ -10508,7 +10510,7 @@
         <v>44822</v>
       </c>
     </row>
-    <row r="358" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
         <v>217</v>
       </c>
@@ -10531,7 +10533,7 @@
         <v>44862</v>
       </c>
     </row>
-    <row r="359" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
         <v>243</v>
       </c>
@@ -10557,7 +10559,7 @@
         <v>33450</v>
       </c>
     </row>
-    <row r="360" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
         <v>243</v>
       </c>
@@ -10583,7 +10585,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="361" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
         <v>243</v>
       </c>
@@ -10609,7 +10611,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="362" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
         <v>243</v>
       </c>
@@ -10635,7 +10637,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="363" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
         <v>243</v>
       </c>
@@ -10661,7 +10663,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="364" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A364" t="s">
         <v>243</v>
       </c>
@@ -10684,7 +10686,7 @@
         <v>37898</v>
       </c>
     </row>
-    <row r="365" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A365" t="s">
         <v>243</v>
       </c>
@@ -10707,7 +10709,7 @@
         <v>38168</v>
       </c>
     </row>
-    <row r="366" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A366" t="s">
         <v>243</v>
       </c>
@@ -10730,7 +10732,7 @@
         <v>38179</v>
       </c>
     </row>
-    <row r="367" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A367" t="s">
         <v>243</v>
       </c>
@@ -10753,7 +10755,7 @@
         <v>38187</v>
       </c>
     </row>
-    <row r="368" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A368" t="s">
         <v>243</v>
       </c>
@@ -10776,7 +10778,7 @@
         <v>38196</v>
       </c>
     </row>
-    <row r="369" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A369" t="s">
         <v>243</v>
       </c>
@@ -10799,7 +10801,7 @@
         <v>38202</v>
       </c>
     </row>
-    <row r="370" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A370" t="s">
         <v>243</v>
       </c>
@@ -10822,7 +10824,7 @@
         <v>38228</v>
       </c>
     </row>
-    <row r="371" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A371" t="s">
         <v>243</v>
       </c>
@@ -10845,7 +10847,7 @@
         <v>38253</v>
       </c>
     </row>
-    <row r="372" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A372" t="s">
         <v>243</v>
       </c>
@@ -10874,7 +10876,7 @@
         <v>39197</v>
       </c>
     </row>
-    <row r="373" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A373" t="s">
         <v>243</v>
       </c>
@@ -10903,7 +10905,7 @@
         <v>39258</v>
       </c>
     </row>
-    <row r="374" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A374" t="s">
         <v>243</v>
       </c>
@@ -10932,7 +10934,7 @@
         <v>39287</v>
       </c>
     </row>
-    <row r="375" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A375" t="s">
         <v>243</v>
       </c>
@@ -10961,7 +10963,7 @@
         <v>39322</v>
       </c>
     </row>
-    <row r="376" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A376" t="s">
         <v>243</v>
       </c>
@@ -10990,7 +10992,7 @@
         <v>39394</v>
       </c>
     </row>
-    <row r="377" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A377" t="s">
         <v>243</v>
       </c>
@@ -11013,7 +11015,7 @@
         <v>39499</v>
       </c>
     </row>
-    <row r="378" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A378" t="s">
         <v>243</v>
       </c>
@@ -11027,7 +11029,7 @@
         <v>39990</v>
       </c>
     </row>
-    <row r="379" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A379" t="s">
         <v>243</v>
       </c>
@@ -11050,7 +11052,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="380" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A380" t="s">
         <v>243</v>
       </c>
@@ -11073,7 +11075,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="381" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A381" t="s">
         <v>243</v>
       </c>
@@ -11096,7 +11098,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="382" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A382" t="s">
         <v>243</v>
       </c>
@@ -11113,7 +11115,7 @@
         <v>40398</v>
       </c>
     </row>
-    <row r="383" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A383" t="s">
         <v>243</v>
       </c>
@@ -11133,7 +11135,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="384" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A384" t="s">
         <v>243</v>
       </c>
@@ -11156,7 +11158,7 @@
         <v>41455</v>
       </c>
     </row>
-    <row r="385" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A385" t="s">
         <v>243</v>
       </c>
@@ -11179,7 +11181,7 @@
         <v>41457</v>
       </c>
     </row>
-    <row r="386" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A386" t="s">
         <v>243</v>
       </c>
@@ -11202,7 +11204,7 @@
         <v>41472</v>
       </c>
     </row>
-    <row r="387" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A387" t="s">
         <v>243</v>
       </c>
@@ -11228,7 +11230,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="388" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A388" t="s">
         <v>243</v>
       </c>
@@ -11251,7 +11253,7 @@
         <v>41488</v>
       </c>
     </row>
-    <row r="389" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A389" t="s">
         <v>243</v>
       </c>
@@ -11277,7 +11279,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="390" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A390" t="s">
         <v>243</v>
       </c>
@@ -11303,7 +11305,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="391" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A391" t="s">
         <v>243</v>
       </c>
@@ -11326,7 +11328,7 @@
         <v>41770</v>
       </c>
     </row>
-    <row r="392" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A392" t="s">
         <v>243</v>
       </c>
@@ -11349,7 +11351,7 @@
         <v>41790</v>
       </c>
     </row>
-    <row r="393" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A393" t="s">
         <v>243</v>
       </c>
@@ -11372,7 +11374,7 @@
         <v>41812</v>
       </c>
     </row>
-    <row r="394" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A394" t="s">
         <v>243</v>
       </c>
@@ -11395,7 +11397,7 @@
         <v>41827</v>
       </c>
     </row>
-    <row r="395" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A395" t="s">
         <v>243</v>
       </c>
@@ -11418,7 +11420,7 @@
         <v>41848</v>
       </c>
     </row>
-    <row r="396" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A396" t="s">
         <v>243</v>
       </c>
@@ -11441,7 +11443,7 @@
         <v>41861</v>
       </c>
     </row>
-    <row r="397" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A397" t="s">
         <v>243</v>
       </c>
@@ -11464,7 +11466,7 @@
         <v>42169</v>
       </c>
     </row>
-    <row r="398" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A398" t="s">
         <v>243</v>
       </c>
@@ -11487,7 +11489,7 @@
         <v>42181</v>
       </c>
     </row>
-    <row r="399" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A399" t="s">
         <v>243</v>
       </c>
@@ -11513,7 +11515,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="400" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A400" t="s">
         <v>243</v>
       </c>
@@ -11536,7 +11538,7 @@
         <v>42226</v>
       </c>
     </row>
-    <row r="401" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A401" t="s">
         <v>243</v>
       </c>
@@ -11559,7 +11561,7 @@
         <v>42252</v>
       </c>
     </row>
-    <row r="402" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A402" t="s">
         <v>243</v>
       </c>
@@ -11582,7 +11584,7 @@
         <v>42539</v>
       </c>
     </row>
-    <row r="403" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A403" t="s">
         <v>243</v>
       </c>
@@ -11605,7 +11607,7 @@
         <v>42576</v>
       </c>
     </row>
-    <row r="404" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A404" t="s">
         <v>243</v>
       </c>
@@ -11628,7 +11630,7 @@
         <v>42883</v>
       </c>
     </row>
-    <row r="405" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A405" t="s">
         <v>243</v>
       </c>
@@ -11654,7 +11656,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="406" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A406" t="s">
         <v>243</v>
       </c>
@@ -11680,7 +11682,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="407" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A407" t="s">
         <v>243</v>
       </c>
@@ -11703,7 +11705,7 @@
         <v>42968</v>
       </c>
     </row>
-    <row r="408" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A408" t="s">
         <v>243</v>
       </c>
@@ -11729,7 +11731,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="409" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A409" t="s">
         <v>243</v>
       </c>
@@ -11752,7 +11754,7 @@
         <v>43290</v>
       </c>
     </row>
-    <row r="410" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A410" t="s">
         <v>243</v>
       </c>
@@ -11778,7 +11780,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="411" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A411" t="s">
         <v>243</v>
       </c>
@@ -11801,7 +11803,7 @@
         <v>43319</v>
       </c>
     </row>
-    <row r="412" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A412" t="s">
         <v>243</v>
       </c>
@@ -11824,7 +11826,7 @@
         <v>43615</v>
       </c>
     </row>
-    <row r="413" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A413" t="s">
         <v>243</v>
       </c>
@@ -11844,7 +11846,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="414" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A414" t="s">
         <v>243</v>
       </c>
@@ -11867,7 +11869,7 @@
         <v>44041</v>
       </c>
     </row>
-    <row r="415" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A415" t="s">
         <v>243</v>
       </c>
@@ -14680,7 +14682,7 @@
         <v>42970</v>
       </c>
     </row>
-    <row r="530" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A530" t="s">
         <v>277</v>
       </c>
@@ -14694,7 +14696,7 @@
         <v>26982</v>
       </c>
     </row>
-    <row r="531" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A531" t="s">
         <v>277</v>
       </c>
@@ -14708,7 +14710,7 @@
         <v>27059</v>
       </c>
     </row>
-    <row r="532" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A532" t="s">
         <v>277</v>
       </c>
@@ -14722,7 +14724,7 @@
         <v>27164</v>
       </c>
     </row>
-    <row r="533" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A533" t="s">
         <v>277</v>
       </c>
@@ -14748,7 +14750,7 @@
         <v>33451</v>
       </c>
     </row>
-    <row r="534" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A534" t="s">
         <v>277</v>
       </c>
@@ -14771,7 +14773,7 @@
         <v>34170</v>
       </c>
     </row>
-    <row r="535" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A535" t="s">
         <v>277</v>
       </c>
@@ -14797,7 +14799,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="536" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A536" t="s">
         <v>277</v>
       </c>
@@ -14823,7 +14825,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="537" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A537" t="s">
         <v>277</v>
       </c>
@@ -14849,7 +14851,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="538" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A538" t="s">
         <v>277</v>
       </c>
@@ -14872,7 +14874,7 @@
         <v>37898</v>
       </c>
     </row>
-    <row r="539" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A539" t="s">
         <v>277</v>
       </c>
@@ -14895,7 +14897,7 @@
         <v>38168</v>
       </c>
     </row>
-    <row r="540" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A540" t="s">
         <v>277</v>
       </c>
@@ -14918,7 +14920,7 @@
         <v>38179</v>
       </c>
     </row>
-    <row r="541" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A541" t="s">
         <v>277</v>
       </c>
@@ -14941,7 +14943,7 @@
         <v>38187</v>
       </c>
     </row>
-    <row r="542" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A542" t="s">
         <v>277</v>
       </c>
@@ -14964,7 +14966,7 @@
         <v>38196</v>
       </c>
     </row>
-    <row r="543" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A543" t="s">
         <v>277</v>
       </c>
@@ -14987,7 +14989,7 @@
         <v>38202</v>
       </c>
     </row>
-    <row r="544" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A544" t="s">
         <v>277</v>
       </c>
@@ -15010,7 +15012,7 @@
         <v>38214</v>
       </c>
     </row>
-    <row r="545" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A545" t="s">
         <v>277</v>
       </c>
@@ -15033,7 +15035,7 @@
         <v>38228</v>
       </c>
     </row>
-    <row r="546" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A546" t="s">
         <v>277</v>
       </c>
@@ -15056,7 +15058,7 @@
         <v>38253</v>
       </c>
     </row>
-    <row r="547" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A547" t="s">
         <v>277</v>
       </c>
@@ -15085,7 +15087,7 @@
         <v>39197</v>
       </c>
     </row>
-    <row r="548" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A548" t="s">
         <v>277</v>
       </c>
@@ -15114,7 +15116,7 @@
         <v>39258</v>
       </c>
     </row>
-    <row r="549" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A549" t="s">
         <v>277</v>
       </c>
@@ -15143,7 +15145,7 @@
         <v>39287</v>
       </c>
     </row>
-    <row r="550" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A550" t="s">
         <v>277</v>
       </c>
@@ -15172,7 +15174,7 @@
         <v>39322</v>
       </c>
     </row>
-    <row r="551" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A551" t="s">
         <v>277</v>
       </c>
@@ -15201,7 +15203,7 @@
         <v>39394</v>
       </c>
     </row>
-    <row r="552" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A552" t="s">
         <v>277</v>
       </c>
@@ -15224,7 +15226,7 @@
         <v>39499</v>
       </c>
     </row>
-    <row r="553" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A553" t="s">
         <v>277</v>
       </c>
@@ -15247,7 +15249,7 @@
         <v>39948</v>
       </c>
     </row>
-    <row r="554" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A554" t="s">
         <v>277</v>
       </c>
@@ -15270,7 +15272,7 @@
         <v>39956</v>
       </c>
     </row>
-    <row r="555" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A555" t="s">
         <v>277</v>
       </c>
@@ -15293,7 +15295,7 @@
         <v>39957</v>
       </c>
     </row>
-    <row r="556" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A556" t="s">
         <v>277</v>
       </c>
@@ -15316,7 +15318,7 @@
         <v>39967</v>
       </c>
     </row>
-    <row r="557" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A557" t="s">
         <v>277</v>
       </c>
@@ -15339,7 +15341,7 @@
         <v>39980</v>
       </c>
     </row>
-    <row r="558" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A558" t="s">
         <v>277</v>
       </c>
@@ -15362,7 +15364,7 @@
         <v>39987</v>
       </c>
     </row>
-    <row r="559" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A559" t="s">
         <v>277</v>
       </c>
@@ -15388,7 +15390,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="560" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A560" t="s">
         <v>277</v>
       </c>
@@ -15411,7 +15413,7 @@
         <v>40017</v>
       </c>
     </row>
-    <row r="561" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A561" t="s">
         <v>277</v>
       </c>
@@ -15434,7 +15436,7 @@
         <v>40036</v>
       </c>
     </row>
-    <row r="562" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A562" t="s">
         <v>277</v>
       </c>
@@ -15457,7 +15459,7 @@
         <v>40069</v>
       </c>
     </row>
-    <row r="563" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A563" t="s">
         <v>277</v>
       </c>
@@ -15480,7 +15482,7 @@
         <v>40329</v>
       </c>
     </row>
-    <row r="564" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A564" t="s">
         <v>277</v>
       </c>
@@ -15503,7 +15505,7 @@
         <v>40349</v>
       </c>
     </row>
-    <row r="565" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A565" t="s">
         <v>277</v>
       </c>
@@ -15526,7 +15528,7 @@
         <v>40361</v>
       </c>
     </row>
-    <row r="566" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A566" t="s">
         <v>277</v>
       </c>
@@ -15549,7 +15551,7 @@
         <v>40375</v>
       </c>
     </row>
-    <row r="567" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A567" t="s">
         <v>277</v>
       </c>
@@ -15572,7 +15574,7 @@
         <v>40389</v>
       </c>
     </row>
-    <row r="568" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A568" t="s">
         <v>277</v>
       </c>
@@ -15580,7 +15582,7 @@
         <v>40405</v>
       </c>
     </row>
-    <row r="569" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A569" t="s">
         <v>277</v>
       </c>
@@ -15603,7 +15605,7 @@
         <v>40412</v>
       </c>
     </row>
-    <row r="570" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A570" t="s">
         <v>277</v>
       </c>
@@ -15626,7 +15628,7 @@
         <v>40670</v>
       </c>
     </row>
-    <row r="571" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A571" t="s">
         <v>277</v>
       </c>
@@ -15652,7 +15654,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="572" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A572" t="s">
         <v>277</v>
       </c>
@@ -15675,7 +15677,7 @@
         <v>40699</v>
       </c>
     </row>
-    <row r="573" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A573" t="s">
         <v>277</v>
       </c>
@@ -15698,7 +15700,7 @@
         <v>40701</v>
       </c>
     </row>
-    <row r="574" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A574" t="s">
         <v>277</v>
       </c>
@@ -15721,7 +15723,7 @@
         <v>40719</v>
       </c>
     </row>
-    <row r="575" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A575" t="s">
         <v>277</v>
       </c>
@@ -15744,7 +15746,7 @@
         <v>40728</v>
       </c>
     </row>
-    <row r="576" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A576" t="s">
         <v>277</v>
       </c>
@@ -15767,7 +15769,7 @@
         <v>40739</v>
       </c>
     </row>
-    <row r="577" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A577" t="s">
         <v>277</v>
       </c>
@@ -15790,7 +15792,7 @@
         <v>40758</v>
       </c>
     </row>
-    <row r="578" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="578" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A578" t="s">
         <v>277</v>
       </c>
@@ -15816,7 +15818,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="579" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="579" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A579" t="s">
         <v>277</v>
       </c>
@@ -15839,7 +15841,7 @@
         <v>40785</v>
       </c>
     </row>
-    <row r="580" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="580" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A580" t="s">
         <v>277</v>
       </c>
@@ -15862,7 +15864,7 @@
         <v>40793</v>
       </c>
     </row>
-    <row r="581" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="581" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A581" t="s">
         <v>277</v>
       </c>
@@ -15885,7 +15887,7 @@
         <v>40814</v>
       </c>
     </row>
-    <row r="582" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A582" t="s">
         <v>277</v>
       </c>
@@ -15908,7 +15910,7 @@
         <v>40822</v>
       </c>
     </row>
-    <row r="583" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="583" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A583" t="s">
         <v>277</v>
       </c>
@@ -15931,7 +15933,7 @@
         <v>41028</v>
       </c>
     </row>
-    <row r="584" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A584" t="s">
         <v>277</v>
       </c>
@@ -15954,7 +15956,7 @@
         <v>41045</v>
       </c>
     </row>
-    <row r="585" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="585" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A585" t="s">
         <v>277</v>
       </c>
@@ -15977,7 +15979,7 @@
         <v>41064</v>
       </c>
     </row>
-    <row r="586" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="586" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A586" t="s">
         <v>277</v>
       </c>
@@ -16000,7 +16002,7 @@
         <v>41085</v>
       </c>
     </row>
-    <row r="587" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="587" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A587" t="s">
         <v>277</v>
       </c>
@@ -16023,7 +16025,7 @@
         <v>41092</v>
       </c>
     </row>
-    <row r="588" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="588" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A588" t="s">
         <v>277</v>
       </c>
@@ -16046,7 +16048,7 @@
         <v>41111</v>
       </c>
     </row>
-    <row r="589" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A589" t="s">
         <v>277</v>
       </c>
@@ -16072,7 +16074,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="590" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="590" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A590" t="s">
         <v>277</v>
       </c>
@@ -16095,7 +16097,7 @@
         <v>41128</v>
       </c>
     </row>
-    <row r="591" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="591" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A591" t="s">
         <v>277</v>
       </c>
@@ -16118,7 +16120,7 @@
         <v>41142</v>
       </c>
     </row>
-    <row r="592" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="592" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A592" t="s">
         <v>277</v>
       </c>
@@ -16141,7 +16143,7 @@
         <v>41167</v>
       </c>
     </row>
-    <row r="593" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="593" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A593" t="s">
         <v>277</v>
       </c>
@@ -16164,7 +16166,7 @@
         <v>41182</v>
       </c>
     </row>
-    <row r="594" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="594" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A594" t="s">
         <v>277</v>
       </c>
@@ -16190,7 +16192,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="595" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="595" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A595" t="s">
         <v>277</v>
       </c>
@@ -16216,7 +16218,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="596" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="596" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A596" t="s">
         <v>277</v>
       </c>
@@ -16239,7 +16241,7 @@
         <v>41450</v>
       </c>
     </row>
-    <row r="597" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="597" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A597" t="s">
         <v>277</v>
       </c>
@@ -16262,7 +16264,7 @@
         <v>41458</v>
       </c>
     </row>
-    <row r="598" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="598" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A598" t="s">
         <v>277</v>
       </c>
@@ -16285,7 +16287,7 @@
         <v>41476</v>
       </c>
     </row>
-    <row r="599" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="599" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A599" t="s">
         <v>277</v>
       </c>
@@ -16308,7 +16310,7 @@
         <v>41492</v>
       </c>
     </row>
-    <row r="600" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="600" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A600" t="s">
         <v>277</v>
       </c>
@@ -16334,7 +16336,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="601" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="601" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A601" t="s">
         <v>277</v>
       </c>
@@ -16360,7 +16362,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="602" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="602" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A602" t="s">
         <v>277</v>
       </c>
@@ -16386,7 +16388,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="603" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="603" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A603" t="s">
         <v>277</v>
       </c>
@@ -16412,7 +16414,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="604" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="604" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A604" t="s">
         <v>277</v>
       </c>
@@ -16438,7 +16440,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="605" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="605" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A605" t="s">
         <v>277</v>
       </c>
@@ -16461,7 +16463,7 @@
         <v>41782</v>
       </c>
     </row>
-    <row r="606" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="606" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A606" t="s">
         <v>277</v>
       </c>
@@ -16487,7 +16489,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="607" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="607" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A607" t="s">
         <v>277</v>
       </c>
@@ -16513,7 +16515,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="608" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="608" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A608" t="s">
         <v>277</v>
       </c>
@@ -16536,7 +16538,7 @@
         <v>41836</v>
       </c>
     </row>
-    <row r="609" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="609" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A609" t="s">
         <v>277</v>
       </c>
@@ -16562,7 +16564,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="610" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="610" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A610" t="s">
         <v>277</v>
       </c>
@@ -16588,7 +16590,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="611" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="611" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A611" t="s">
         <v>277</v>
       </c>
@@ -16614,7 +16616,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="612" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="612" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A612" t="s">
         <v>277</v>
       </c>
@@ -16640,7 +16642,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="613" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="613" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A613" t="s">
         <v>277</v>
       </c>
@@ -16666,7 +16668,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="614" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="614" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A614" t="s">
         <v>277</v>
       </c>
@@ -16692,7 +16694,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="615" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="615" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A615" t="s">
         <v>277</v>
       </c>
@@ -16718,7 +16720,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="616" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="616" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A616" t="s">
         <v>277</v>
       </c>
@@ -16744,7 +16746,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="617" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="617" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A617" t="s">
         <v>277</v>
       </c>
@@ -16770,7 +16772,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="618" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="618" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A618" t="s">
         <v>277</v>
       </c>
@@ -16796,7 +16798,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="619" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="619" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A619" t="s">
         <v>277</v>
       </c>
@@ -16822,7 +16824,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="620" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="620" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A620" t="s">
         <v>277</v>
       </c>
@@ -16848,7 +16850,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="621" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="621" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A621" t="s">
         <v>277</v>
       </c>
@@ -16871,7 +16873,7 @@
         <v>42299</v>
       </c>
     </row>
-    <row r="622" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="622" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A622" t="s">
         <v>277</v>
       </c>
@@ -16894,7 +16896,7 @@
         <v>45078</v>
       </c>
     </row>
-    <row r="623" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="623" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A623" t="s">
         <v>277</v>
       </c>
@@ -16920,7 +16922,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="624" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="624" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A624" t="s">
         <v>277</v>
       </c>
@@ -16943,7 +16945,7 @@
         <v>45222</v>
       </c>
     </row>
-    <row r="625" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="625" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A625" t="s">
         <v>277</v>
       </c>
@@ -16966,7 +16968,7 @@
         <v>45206</v>
       </c>
     </row>
-    <row r="626" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="626" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A626" t="s">
         <v>277</v>
       </c>
@@ -16989,7 +16991,7 @@
         <v>45195</v>
       </c>
     </row>
-    <row r="627" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="627" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A627" t="s">
         <v>277</v>
       </c>
@@ -17012,7 +17014,7 @@
         <v>45190</v>
       </c>
     </row>
-    <row r="628" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="628" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A628" t="s">
         <v>277</v>
       </c>
@@ -17035,7 +17037,7 @@
         <v>45174</v>
       </c>
     </row>
-    <row r="629" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="629" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A629" t="s">
         <v>277</v>
       </c>
@@ -17058,7 +17060,7 @@
         <v>45165</v>
       </c>
     </row>
-    <row r="630" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="630" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A630" t="s">
         <v>277</v>
       </c>
@@ -17081,7 +17083,7 @@
         <v>45158</v>
       </c>
     </row>
-    <row r="631" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="631" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A631" t="s">
         <v>277</v>
       </c>
@@ -17104,7 +17106,7 @@
         <v>45142</v>
       </c>
     </row>
-    <row r="632" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="632" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A632" t="s">
         <v>277</v>
       </c>
@@ -17127,7 +17129,7 @@
         <v>45126</v>
       </c>
     </row>
-    <row r="633" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="633" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A633" t="s">
         <v>277</v>
       </c>
@@ -17150,7 +17152,7 @@
         <v>45110</v>
       </c>
     </row>
-    <row r="634" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="634" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A634" t="s">
         <v>277</v>
       </c>
@@ -17173,7 +17175,7 @@
         <v>45092</v>
       </c>
     </row>
-    <row r="635" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="635" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A635" t="s">
         <v>59</v>
       </c>
@@ -17196,7 +17198,7 @@
         <v>45206</v>
       </c>
     </row>
-    <row r="636" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="636" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A636" t="s">
         <v>59</v>
       </c>
@@ -17219,7 +17221,7 @@
         <v>45195</v>
       </c>
     </row>
-    <row r="637" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="637" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A637" t="s">
         <v>59</v>
       </c>
@@ -17242,7 +17244,7 @@
         <v>45190</v>
       </c>
     </row>
-    <row r="638" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="638" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A638" t="s">
         <v>59</v>
       </c>
@@ -17265,7 +17267,7 @@
         <v>45174</v>
       </c>
     </row>
-    <row r="639" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="639" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A639" t="s">
         <v>59</v>
       </c>
@@ -17288,7 +17290,7 @@
         <v>45167</v>
       </c>
     </row>
-    <row r="640" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="640" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A640" t="s">
         <v>59</v>
       </c>
@@ -17308,7 +17310,7 @@
         <v>45165</v>
       </c>
     </row>
-    <row r="641" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="641" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A641" t="s">
         <v>59</v>
       </c>
@@ -17331,7 +17333,7 @@
         <v>45141</v>
       </c>
     </row>
-    <row r="642" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="642" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A642" t="s">
         <v>59</v>
       </c>
@@ -17354,7 +17356,7 @@
         <v>45133</v>
       </c>
     </row>
-    <row r="643" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="643" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A643" t="s">
         <v>59</v>
       </c>
@@ -17374,7 +17376,7 @@
         <v>45131</v>
       </c>
     </row>
-    <row r="644" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="644" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A644" t="s">
         <v>59</v>
       </c>
@@ -17397,7 +17399,7 @@
         <v>45110</v>
       </c>
     </row>
-    <row r="645" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="645" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A645" t="s">
         <v>59</v>
       </c>
@@ -17417,7 +17419,7 @@
         <v>45103</v>
       </c>
     </row>
-    <row r="646" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="646" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A646" t="s">
         <v>59</v>
       </c>
@@ -17440,7 +17442,7 @@
         <v>45092</v>
       </c>
     </row>
-    <row r="647" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="647" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A647" t="s">
         <v>59</v>
       </c>
@@ -17463,7 +17465,7 @@
         <v>45078</v>
       </c>
     </row>
-    <row r="648" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="648" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A648" t="s">
         <v>59</v>
       </c>
@@ -17492,7 +17494,7 @@
         <v>45062</v>
       </c>
     </row>
-    <row r="649" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="649" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A649" t="s">
         <v>277</v>
       </c>
@@ -17512,7 +17514,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="650" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="650" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A650" t="s">
         <v>277</v>
       </c>
@@ -17532,7 +17534,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="651" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="651" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A651" t="s">
         <v>277</v>
       </c>
@@ -17552,7 +17554,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="652" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="652" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A652" t="s">
         <v>277</v>
       </c>
@@ -17572,7 +17574,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="653" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="653" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A653" t="s">
         <v>277</v>
       </c>
@@ -17592,7 +17594,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="654" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="654" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A654" t="s">
         <v>277</v>
       </c>
@@ -17612,7 +17614,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="655" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="655" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A655" t="s">
         <v>59</v>
       </c>
@@ -17632,7 +17634,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="656" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="656" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A656" t="s">
         <v>59</v>
       </c>
@@ -17652,7 +17654,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="657" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="657" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A657" t="s">
         <v>59</v>
       </c>
@@ -17672,7 +17674,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="658" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="658" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A658" t="s">
         <v>59</v>
       </c>
@@ -17692,7 +17694,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="659" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="659" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A659" t="s">
         <v>59</v>
       </c>
@@ -17712,7 +17714,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="660" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="660" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A660" t="s">
         <v>59</v>
       </c>
@@ -17732,7 +17734,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="661" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="661" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A661" t="s">
         <v>217</v>
       </c>
@@ -17752,7 +17754,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="662" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="662" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A662" t="s">
         <v>243</v>
       </c>
@@ -17772,7 +17774,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="663" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="663" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A663" t="s">
         <v>0</v>
       </c>
@@ -17792,7 +17794,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="664" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="664" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A664" t="s">
         <v>0</v>
       </c>
@@ -17818,7 +17820,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="665" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="665" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A665" t="s">
         <v>217</v>
       </c>
@@ -17844,7 +17846,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="666" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="666" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A666" t="s">
         <v>217</v>
       </c>
@@ -17870,7 +17872,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="667" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="667" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A667" t="s">
         <v>217</v>
       </c>
@@ -17896,7 +17898,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="668" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="668" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A668" t="s">
         <v>217</v>
       </c>
@@ -17922,7 +17924,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="669" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="669" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A669" t="s">
         <v>217</v>
       </c>
@@ -17948,7 +17950,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="670" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="670" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A670" t="s">
         <v>277</v>
       </c>
@@ -17970,8 +17972,11 @@
       <c r="K670" s="1">
         <v>45366</v>
       </c>
-    </row>
-    <row r="671" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+      <c r="L670" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="671" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A671" t="s">
         <v>277</v>
       </c>
@@ -17993,8 +17998,11 @@
       <c r="K671" s="1">
         <v>45473</v>
       </c>
-    </row>
-    <row r="672" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+      <c r="L671" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="672" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A672" t="s">
         <v>277</v>
       </c>
@@ -18016,8 +18024,11 @@
       <c r="K672" s="1">
         <v>45515</v>
       </c>
-    </row>
-    <row r="673" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+      <c r="L672" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="673" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A673" t="s">
         <v>59</v>
       </c>
@@ -18039,8 +18050,11 @@
       <c r="K673" s="1">
         <v>45562</v>
       </c>
-    </row>
-    <row r="674" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+      <c r="L673" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="674" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A674" t="s">
         <v>59</v>
       </c>
@@ -18062,8 +18076,11 @@
       <c r="K674" s="1">
         <v>45551</v>
       </c>
-    </row>
-    <row r="675" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+      <c r="L674" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="675" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A675" t="s">
         <v>59</v>
       </c>
@@ -18097,8 +18114,11 @@
       <c r="K675" s="1">
         <v>45544</v>
       </c>
-    </row>
-    <row r="676" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+      <c r="L675" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="676" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A676" t="s">
         <v>59</v>
       </c>
@@ -18120,8 +18140,11 @@
       <c r="K676" s="1">
         <v>45532</v>
       </c>
-    </row>
-    <row r="677" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+      <c r="L676" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="677" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A677" t="s">
         <v>59</v>
       </c>
@@ -18155,8 +18178,11 @@
       <c r="K677" s="1">
         <v>45502</v>
       </c>
-    </row>
-    <row r="678" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+      <c r="L677" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="678" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A678" t="s">
         <v>59</v>
       </c>
@@ -18178,8 +18204,11 @@
       <c r="K678" s="1">
         <v>45485</v>
       </c>
-    </row>
-    <row r="679" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+      <c r="L678" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="679" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A679" t="s">
         <v>59</v>
       </c>
@@ -18213,15 +18242,399 @@
       <c r="K679" s="1">
         <v>45454</v>
       </c>
+      <c r="L679" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="680" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A680" t="s">
+        <v>217</v>
+      </c>
+      <c r="B680">
+        <v>21</v>
+      </c>
+      <c r="C680" t="s">
+        <v>1</v>
+      </c>
+      <c r="D680">
+        <v>33</v>
+      </c>
+      <c r="I680" t="s">
+        <v>6</v>
+      </c>
+      <c r="J680" t="s">
+        <v>477</v>
+      </c>
+      <c r="K680" s="1">
+        <v>45942</v>
+      </c>
+      <c r="L680" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="681" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A681" t="s">
+        <v>217</v>
+      </c>
+      <c r="B681">
+        <v>23</v>
+      </c>
+      <c r="C681" t="s">
+        <v>1</v>
+      </c>
+      <c r="D681">
+        <v>32</v>
+      </c>
+      <c r="I681" t="s">
+        <v>6</v>
+      </c>
+      <c r="J681" t="s">
+        <v>477</v>
+      </c>
+      <c r="K681" s="1">
+        <v>45934</v>
+      </c>
+      <c r="L681" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="682" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A682" t="s">
+        <v>217</v>
+      </c>
+      <c r="B682">
+        <v>21</v>
+      </c>
+      <c r="C682" t="s">
+        <v>1</v>
+      </c>
+      <c r="D682">
+        <v>33</v>
+      </c>
+      <c r="I682" t="s">
+        <v>6</v>
+      </c>
+      <c r="J682" t="s">
+        <v>477</v>
+      </c>
+      <c r="K682" s="1">
+        <v>45926</v>
+      </c>
+      <c r="L682" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="683" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A683" t="s">
+        <v>217</v>
+      </c>
+      <c r="B683">
+        <v>18</v>
+      </c>
+      <c r="C683" t="s">
+        <v>1</v>
+      </c>
+      <c r="D683">
+        <v>35</v>
+      </c>
+      <c r="I683" t="s">
+        <v>6</v>
+      </c>
+      <c r="J683" t="s">
+        <v>477</v>
+      </c>
+      <c r="K683" s="1">
+        <v>45878</v>
+      </c>
+      <c r="L683" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="684" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A684" t="s">
+        <v>217</v>
+      </c>
+      <c r="B684">
+        <v>22</v>
+      </c>
+      <c r="C684" t="s">
+        <v>1</v>
+      </c>
+      <c r="D684">
+        <v>33</v>
+      </c>
+      <c r="I684" t="s">
+        <v>6</v>
+      </c>
+      <c r="J684" t="s">
+        <v>477</v>
+      </c>
+      <c r="K684" s="1">
+        <v>45830</v>
+      </c>
+      <c r="L684" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="685" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A685" t="s">
+        <v>217</v>
+      </c>
+      <c r="B685">
+        <v>28</v>
+      </c>
+      <c r="C685" t="s">
+        <v>1</v>
+      </c>
+      <c r="D685">
+        <v>29</v>
+      </c>
+      <c r="I685" t="s">
+        <v>6</v>
+      </c>
+      <c r="J685" t="s">
+        <v>477</v>
+      </c>
+      <c r="K685" s="1">
+        <v>45806</v>
+      </c>
+      <c r="L685" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="686" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A686" t="s">
+        <v>217</v>
+      </c>
+      <c r="B686">
+        <v>26</v>
+      </c>
+      <c r="C686" t="s">
+        <v>1</v>
+      </c>
+      <c r="D686">
+        <v>30</v>
+      </c>
+      <c r="I686" t="s">
+        <v>6</v>
+      </c>
+      <c r="J686" t="s">
+        <v>477</v>
+      </c>
+      <c r="K686" s="1">
+        <v>45790</v>
+      </c>
+      <c r="L686" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="687" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A687" t="s">
+        <v>277</v>
+      </c>
+      <c r="B687">
+        <v>23</v>
+      </c>
+      <c r="C687" t="s">
+        <v>1</v>
+      </c>
+      <c r="D687">
+        <v>32</v>
+      </c>
+      <c r="I687" t="s">
+        <v>6</v>
+      </c>
+      <c r="J687" t="s">
+        <v>477</v>
+      </c>
+      <c r="K687" s="1">
+        <v>45898</v>
+      </c>
+      <c r="L687" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="688" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A688" t="s">
+        <v>277</v>
+      </c>
+      <c r="B688">
+        <v>17</v>
+      </c>
+      <c r="C688" t="s">
+        <v>1</v>
+      </c>
+      <c r="D688">
+        <v>36</v>
+      </c>
+      <c r="I688" t="s">
+        <v>6</v>
+      </c>
+      <c r="J688" t="s">
+        <v>477</v>
+      </c>
+      <c r="K688" s="1">
+        <v>45872</v>
+      </c>
+      <c r="L688" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="689" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A689" t="s">
+        <v>277</v>
+      </c>
+      <c r="B689">
+        <v>19.5</v>
+      </c>
+      <c r="C689" t="s">
+        <v>1</v>
+      </c>
+      <c r="D689">
+        <v>34</v>
+      </c>
+      <c r="I689" t="s">
+        <v>6</v>
+      </c>
+      <c r="J689" t="s">
+        <v>477</v>
+      </c>
+      <c r="K689" s="1">
+        <v>45841</v>
+      </c>
+      <c r="L689" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="690" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A690" t="s">
+        <v>277</v>
+      </c>
+      <c r="B690">
+        <v>18.5</v>
+      </c>
+      <c r="C690" t="s">
+        <v>1</v>
+      </c>
+      <c r="D690">
+        <v>35</v>
+      </c>
+      <c r="I690" t="s">
+        <v>6</v>
+      </c>
+      <c r="J690" t="s">
+        <v>477</v>
+      </c>
+      <c r="K690" s="1">
+        <v>45777</v>
+      </c>
+      <c r="L690" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="691" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A691" t="s">
+        <v>59</v>
+      </c>
+      <c r="B691">
+        <v>14</v>
+      </c>
+      <c r="C691" t="s">
+        <v>1</v>
+      </c>
+      <c r="E691">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="F691">
+        <v>49</v>
+      </c>
+      <c r="G691">
+        <v>3.17</v>
+      </c>
+      <c r="H691">
+        <v>44</v>
+      </c>
+      <c r="K691" s="1">
+        <v>45907</v>
+      </c>
+    </row>
+    <row r="692" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A692" t="s">
+        <v>59</v>
+      </c>
+      <c r="B692">
+        <v>16.5</v>
+      </c>
+      <c r="C692" t="s">
+        <v>1</v>
+      </c>
+      <c r="E692">
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="F692">
+        <v>48</v>
+      </c>
+      <c r="G692">
+        <v>1.51</v>
+      </c>
+      <c r="H692">
+        <v>38</v>
+      </c>
+      <c r="I692" t="s">
+        <v>55</v>
+      </c>
+      <c r="K692" s="1">
+        <v>45867</v>
+      </c>
+    </row>
+    <row r="693" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A693" t="s">
+        <v>59</v>
+      </c>
+      <c r="B693">
+        <v>14</v>
+      </c>
+      <c r="C693" t="s">
+        <v>1</v>
+      </c>
+      <c r="E693">
+        <v>1.6E-2</v>
+      </c>
+      <c r="F693">
+        <v>50</v>
+      </c>
+      <c r="G693">
+        <v>2.8</v>
+      </c>
+      <c r="H693">
+        <v>43</v>
+      </c>
+      <c r="K693" s="1">
+        <v>45831</v>
+      </c>
+      <c r="L693" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="694" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A694" t="s">
+        <v>59</v>
+      </c>
+      <c r="C694" t="s">
+        <v>1</v>
+      </c>
+      <c r="E694">
+        <v>2.3E-2</v>
+      </c>
+      <c r="F694">
+        <v>52</v>
+      </c>
+      <c r="K694" s="1">
+        <v>45796</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L679">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="Muskellunge Lake"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:L690"/>
   <sortState ref="A2:Q625">
     <sortCondition ref="A2:A625"/>
   </sortState>
